--- a/reports/集团总公司_成本费用表_2025.xlsx
+++ b/reports/集团总公司_成本费用表_2025.xlsx
@@ -5463,7 +5463,7 @@
       <c r="H61" s="17" t="n"/>
       <c r="I61" s="17" t="n"/>
       <c r="J61" s="14" t="n">
-        <v>4193660</v>
+        <v>34193660</v>
       </c>
       <c r="K61" s="14" t="n">
         <v>0</v>
